--- a/artfynd/S 450-2026 artfynd.xlsx
+++ b/artfynd/S 450-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822665</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822666</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822671</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822707</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822929</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822931</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822932</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822933</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822935</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822962</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822963</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822965</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088814</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2529,6 +2614,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088963</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2650,6 +2740,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088964</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2771,6 +2866,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088966</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088969</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088602</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3134,6 +3244,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088608</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3255,6 +3370,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3376,6 +3496,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089101</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3497,6 +3622,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089102</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3618,6 +3748,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089103</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3739,6 +3874,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089137</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3860,6 +4000,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089138</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3981,6 +4126,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089146</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4088,6 +4238,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823125</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4204,6 +4359,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131166211</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4320,6 +4480,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131166213</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4436,6 +4601,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131166210</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4552,6 +4722,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824397</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4668,6 +4843,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824396</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4788,6 +4968,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824403</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4914,6 +5099,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824415</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5035,6 +5225,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824427</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5161,6 +5356,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133824432</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5277,6 +5477,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822994</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5384,6 +5589,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823084</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5491,6 +5701,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133823085</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5598,6 +5813,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822754</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5705,6 +5925,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822756</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5812,6 +6037,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822765</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5924,6 +6154,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822766</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6036,6 +6271,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822777</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6148,6 +6388,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822783</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6255,6 +6500,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822792</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6362,6 +6612,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822854</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6469,6 +6724,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822712</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6590,6 +6850,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088900</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6711,6 +6976,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088901</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6832,6 +7102,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088902</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6953,6 +7228,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088930</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7074,6 +7354,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088931</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7195,6 +7480,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088932</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7316,6 +7606,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088933</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7437,6 +7732,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088934</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7558,6 +7858,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088967</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7679,6 +7984,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089097</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7800,6 +8110,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089135</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7912,6 +8227,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822753</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8019,6 +8339,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822775</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8126,6 +8451,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822776</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8233,6 +8563,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822784</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8340,6 +8675,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822789</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8447,6 +8787,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822790</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8554,6 +8899,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822791</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8661,8 +9011,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822818</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 450-2026 artfynd.xlsx
+++ b/artfynd/S 450-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6732,27 +6732,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131088900</v>
+        <v>136289084</v>
       </c>
       <c r="B53" t="n">
-        <v>58327</v>
+        <v>57987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6760,14 +6760,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6777,17 +6775,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bastvålen, Östmark, Vrm</t>
+          <t>N2000, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385475</v>
+        <v>386611</v>
       </c>
       <c r="R53" t="n">
         <v>6684132</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6811,22 +6809,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6841,24 +6839,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Vivian Nielsen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Annelie Thor</t>
+          <t>Vivian Nielsen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088900</t>
+          <t>https://artportalen.se/Sighting/136289084</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131088901</v>
+        <v>131088900</v>
       </c>
       <c r="B54" t="n">
         <v>58327</v>
@@ -6907,10 +6905,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385474</v>
+        <v>385475</v>
       </c>
       <c r="R54" t="n">
-        <v>6684407</v>
+        <v>6684132</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6942,7 +6940,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6952,7 +6950,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6978,13 +6976,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088901</t>
+          <t>https://artportalen.se/Sighting/131088900</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131088902</v>
+        <v>131088901</v>
       </c>
       <c r="B55" t="n">
         <v>58327</v>
@@ -7033,10 +7031,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385446</v>
+        <v>385474</v>
       </c>
       <c r="R55" t="n">
-        <v>6684413</v>
+        <v>6684407</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7068,7 +7066,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7078,7 +7076,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7104,13 +7102,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088902</t>
+          <t>https://artportalen.se/Sighting/131088901</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131088930</v>
+        <v>131088902</v>
       </c>
       <c r="B56" t="n">
         <v>58327</v>
@@ -7159,10 +7157,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385396</v>
+        <v>385446</v>
       </c>
       <c r="R56" t="n">
-        <v>6684329</v>
+        <v>6684413</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7189,22 +7187,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>03:26</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>03:26</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7230,13 +7228,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088930</t>
+          <t>https://artportalen.se/Sighting/131088902</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131088931</v>
+        <v>131088930</v>
       </c>
       <c r="B57" t="n">
         <v>58327</v>
@@ -7285,10 +7283,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385404</v>
+        <v>385396</v>
       </c>
       <c r="R57" t="n">
-        <v>6684302</v>
+        <v>6684329</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7320,7 +7318,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>03:17</t>
+          <t>03:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7330,7 +7328,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>03:17</t>
+          <t>03:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7356,13 +7354,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088931</t>
+          <t>https://artportalen.se/Sighting/131088930</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131088932</v>
+        <v>131088931</v>
       </c>
       <c r="B58" t="n">
         <v>58327</v>
@@ -7397,7 +7395,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -7411,10 +7409,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385450</v>
+        <v>385404</v>
       </c>
       <c r="R58" t="n">
-        <v>6684206</v>
+        <v>6684302</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7446,7 +7444,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7456,7 +7454,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7482,13 +7480,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088932</t>
+          <t>https://artportalen.se/Sighting/131088931</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131088933</v>
+        <v>131088932</v>
       </c>
       <c r="B59" t="n">
         <v>58327</v>
@@ -7523,7 +7521,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -7537,10 +7535,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385481</v>
+        <v>385450</v>
       </c>
       <c r="R59" t="n">
-        <v>6684125</v>
+        <v>6684206</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7572,7 +7570,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>02:52</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7582,7 +7580,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>02:52</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7608,13 +7606,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088933</t>
+          <t>https://artportalen.se/Sighting/131088932</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131088934</v>
+        <v>131088933</v>
       </c>
       <c r="B60" t="n">
         <v>58327</v>
@@ -7663,10 +7661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385533</v>
+        <v>385481</v>
       </c>
       <c r="R60" t="n">
-        <v>6684040</v>
+        <v>6684125</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7698,7 +7696,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>02:43</t>
+          <t>02:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7708,7 +7706,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>02:43</t>
+          <t>02:52</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7734,13 +7732,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088934</t>
+          <t>https://artportalen.se/Sighting/131088933</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131088967</v>
+        <v>131088934</v>
       </c>
       <c r="B61" t="n">
         <v>58327</v>
@@ -7789,10 +7787,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385249</v>
+        <v>385533</v>
       </c>
       <c r="R61" t="n">
-        <v>6684370</v>
+        <v>6684040</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7819,22 +7817,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>02:49</t>
+          <t>02:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>02:49</t>
+          <t>02:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7860,16 +7858,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131088967</t>
+          <t>https://artportalen.se/Sighting/131088934</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131089097</v>
+        <v>131088967</v>
       </c>
       <c r="B62" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7877,16 +7875,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7915,10 +7913,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385452</v>
+        <v>385249</v>
       </c>
       <c r="R62" t="n">
-        <v>6684085</v>
+        <v>6684370</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7945,22 +7943,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>02:47</t>
+          <t>02:49</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>02:47</t>
+          <t>02:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7986,13 +7984,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131089097</t>
+          <t>https://artportalen.se/Sighting/131088967</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131089135</v>
+        <v>131089097</v>
       </c>
       <c r="B63" t="n">
         <v>58636</v>
@@ -8027,7 +8025,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8041,10 +8039,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385358</v>
+        <v>385452</v>
       </c>
       <c r="R63" t="n">
-        <v>6684159</v>
+        <v>6684085</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8071,22 +8069,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>02:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>02:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8112,16 +8110,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131089135</t>
+          <t>https://artportalen.se/Sighting/131089097</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133822753</v>
+        <v>131089135</v>
       </c>
       <c r="B64" t="n">
-        <v>98060</v>
+        <v>58636</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8129,34 +8127,48 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bastvålen, Östmark, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385265</v>
+        <v>385358</v>
       </c>
       <c r="R64" t="n">
-        <v>6684263</v>
+        <v>6684159</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8183,27 +8195,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>yta ca 1×1m</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8229,13 +8236,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822753</t>
+          <t>https://artportalen.se/Sighting/131089135</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133822775</v>
+        <v>133822753</v>
       </c>
       <c r="B65" t="n">
         <v>98060</v>
@@ -8270,10 +8277,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385292</v>
+        <v>385265</v>
       </c>
       <c r="R65" t="n">
-        <v>6684222</v>
+        <v>6684263</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8305,7 +8312,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>07:04</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8315,7 +8322,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>07:04</t>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>yta ca 1×1m</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8341,13 +8353,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822775</t>
+          <t>https://artportalen.se/Sighting/133822753</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133822776</v>
+        <v>133822775</v>
       </c>
       <c r="B66" t="n">
         <v>98060</v>
@@ -8382,10 +8394,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385198</v>
+        <v>385292</v>
       </c>
       <c r="R66" t="n">
-        <v>6684307</v>
+        <v>6684222</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8417,7 +8429,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8427,7 +8439,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8453,13 +8465,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822776</t>
+          <t>https://artportalen.se/Sighting/133822775</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133822784</v>
+        <v>133822776</v>
       </c>
       <c r="B67" t="n">
         <v>98060</v>
@@ -8494,10 +8506,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385256</v>
+        <v>385198</v>
       </c>
       <c r="R67" t="n">
-        <v>6684246</v>
+        <v>6684307</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8524,22 +8536,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8565,13 +8577,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822784</t>
+          <t>https://artportalen.se/Sighting/133822776</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133822789</v>
+        <v>133822784</v>
       </c>
       <c r="B68" t="n">
         <v>98060</v>
@@ -8606,10 +8618,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385291</v>
+        <v>385256</v>
       </c>
       <c r="R68" t="n">
-        <v>6684172</v>
+        <v>6684246</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8636,22 +8648,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8671,19 +8683,19 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore</t>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822789</t>
+          <t>https://artportalen.se/Sighting/133822784</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133822790</v>
+        <v>133822789</v>
       </c>
       <c r="B69" t="n">
         <v>98060</v>
@@ -8718,10 +8730,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385316</v>
+        <v>385291</v>
       </c>
       <c r="R69" t="n">
-        <v>6684166</v>
+        <v>6684172</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8753,7 +8765,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8763,7 +8775,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8789,13 +8801,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822790</t>
+          <t>https://artportalen.se/Sighting/133822789</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133822791</v>
+        <v>133822790</v>
       </c>
       <c r="B70" t="n">
         <v>98060</v>
@@ -8830,10 +8842,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385297</v>
+        <v>385316</v>
       </c>
       <c r="R70" t="n">
-        <v>6684220</v>
+        <v>6684166</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8865,7 +8877,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8875,7 +8887,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8901,16 +8913,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133822791</t>
+          <t>https://artportalen.se/Sighting/133822790</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133822818</v>
+        <v>133822791</v>
       </c>
       <c r="B71" t="n">
-        <v>99001</v>
+        <v>98060</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8918,16 +8930,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223049</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8942,10 +8954,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385231</v>
+        <v>385297</v>
       </c>
       <c r="R71" t="n">
-        <v>6684252</v>
+        <v>6684220</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8977,7 +8989,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8987,7 +8999,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9007,11 +9019,123 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eduardo Ottimofiore, Annelie Thor</t>
+          <t>Eduardo Ottimofiore</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822791</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>133822818</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>385231</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6684252</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133822818</t>
         </is>
@@ -9089,6 +9213,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 450-2026 artfynd.xlsx
+++ b/artfynd/S 450-2026 artfynd.xlsx
@@ -6735,7 +6735,7 @@
         <v>136289084</v>
       </c>
       <c r="B53" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
